--- a/diseases/d091/2005-2009.xlsx
+++ b/diseases/d091/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1451,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -2001,9 +1992,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2137,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -2693,9 +2678,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2841,9 +2823,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3385,9 +3364,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3533,9 +3509,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -4077,9 +4050,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4225,9 +4195,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4769,9 +4736,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4917,9 +4881,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5461,9 +5422,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5609,9 +5567,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6153,9 +6108,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6301,9 +6253,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6845,9 +6794,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6993,9 +6939,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7537,9 +7480,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7685,9 +7625,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8229,9 +8166,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8377,9 +8311,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9069,9 +9000,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9217,9 +9145,6 @@
       <c r="O51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -9761,9 +9686,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10157,9 +10079,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10305,9 +10224,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10849,9 +10765,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10997,9 +10910,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11541,9 +11451,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11689,9 +11596,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -12233,9 +12137,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12381,9 +12282,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12925,9 +12823,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13073,9 +12968,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13765,9 +13657,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -13913,9 +13802,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14457,9 +14343,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14605,9 +14488,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15149,9 +15029,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15297,9 +15174,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -15841,9 +15715,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15989,9 +15860,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16533,9 +16401,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16681,9 +16546,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17225,9 +17087,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17373,9 +17232,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17917,9 +17773,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18065,9 +17918,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18609,9 +18459,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -19005,9 +18852,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19301,9 +19145,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19597,9 +19438,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19893,9 +19731,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20189,9 +20024,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20633,9 +20465,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20929,9 +20758,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21373,9 +21199,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -21669,9 +21492,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22113,9 +21933,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22557,9 +22374,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23001,9 +22815,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -23445,9 +23256,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -23841,9 +23649,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24137,9 +23942,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -24581,9 +24383,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25025,9 +24824,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -25469,9 +25265,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -25765,9 +25558,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -26209,9 +25999,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26653,9 +26440,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27097,9 +26881,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -27541,9 +27322,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -27985,9 +27763,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -28429,9 +28204,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -29021,9 +28793,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -29417,9 +29186,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -29861,9 +29627,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -30453,9 +30216,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -31193,9 +30953,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -31637,9 +31394,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -32081,9 +31835,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -32525,9 +32276,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -33117,9 +32865,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -33709,9 +33454,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -34301,9 +34043,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -34893,9 +34632,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -35483,9 +35219,6 @@
         <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
